--- a/scripts/checks/results/HLR_results_04_>1_lg_families_tPBC.xlsx
+++ b/scripts/checks/results/HLR_results_04_>1_lg_families_tPBC.xlsx
@@ -553,66 +553,66 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>1486</v>
+        <v>1805</v>
       </c>
       <c r="E2" t="n">
-        <v>1484</v>
+        <v>1803</v>
       </c>
       <c r="F2" t="n">
         <v>1</v>
       </c>
       <c r="G2" t="n">
-        <v>0.2832518542518089</v>
+        <v>0.2289660427374866</v>
       </c>
       <c r="H2" t="n">
-        <v>586.4622799559509</v>
+        <v>535.4184094840506</v>
       </c>
       <c r="I2" t="n">
-        <v>1.867790180999188e-109</v>
+        <v>6.165311118376326e-104</v>
       </c>
       <c r="J2" t="n">
-        <v>166.4167646289528</v>
+        <v>204.972863262423</v>
       </c>
       <c r="K2" t="n">
-        <v>232.1830417227456</v>
+        <v>265.8415512465374</v>
       </c>
       <c r="L2" t="n">
-        <v>65.76627709379278</v>
+        <v>60.86868798411442</v>
       </c>
       <c r="M2" t="n">
-        <v>0.1121406769736879</v>
+        <v>0.113684339025193</v>
       </c>
       <c r="N2" t="n">
-        <v>0.1563522166483135</v>
+        <v>0.1473622789614952</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>{'const': 0.7273505426173328, 'N1ratio-ArgsPreds': -0.20746099596041467}</t>
+          <t>{'const': 0.5718717535467436, 'N1ratio-ArgsPreds': -2.218404205002331}</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>{'const': 9.29807944785156e-161, 'N1ratio-ArgsPreds': 1.867790180997848e-109}</t>
+          <t>{'const': 1.6885341073455672e-165, 'N1ratio-ArgsPreds': 6.1653111183735e-104}</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': -0.5322141056490415}</t>
+          <t>{'N1ratio-ArgsPreds': -0.478503963136657}</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': np.float64(-0.5322141056490425)}</t>
+          <t>{'N1ratio-ArgsPreds': np.float64(-0.4785039631366576)}</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': np.float64(-0.5322141056490424)}</t>
+          <t>{'N1ratio-ArgsPreds': np.float64(-0.47850396313665755)}</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': np.float64(28.325185425181004)}</t>
+          <t>{'N1ratio-ArgsPreds': np.float64(22.89660427374877)}</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
@@ -628,80 +628,80 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>['N1ratio-ArgsPreds', 'latitude', 'longitude', 'Macro_class']</t>
+          <t>['N1ratio-ArgsPreds', 'Macro_class']</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>1486</v>
+        <v>1805</v>
       </c>
       <c r="E3" t="n">
-        <v>1481</v>
+        <v>1802</v>
       </c>
       <c r="F3" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G3" t="n">
-        <v>0.343362345027855</v>
+        <v>0.2665509883761625</v>
       </c>
       <c r="H3" t="n">
-        <v>193.6073986679248</v>
+        <v>327.4425852660282</v>
       </c>
       <c r="I3" t="n">
-        <v>1.370015064749427e-133</v>
+        <v>4.992347745244783e-122</v>
       </c>
       <c r="J3" t="n">
-        <v>152.4601280411233</v>
+        <v>194.9812230103206</v>
       </c>
       <c r="K3" t="n">
-        <v>232.1830417227456</v>
+        <v>265.8415512465374</v>
       </c>
       <c r="L3" t="n">
-        <v>19.93072842040556</v>
+        <v>35.43016411810841</v>
       </c>
       <c r="M3" t="n">
-        <v>0.1029440432418118</v>
+        <v>0.1082026764763155</v>
       </c>
       <c r="N3" t="n">
-        <v>0.1563522166483135</v>
+        <v>0.1473622789614952</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>{'const': 0.5931981450813734, 'N1ratio-ArgsPreds': -0.2114124485447942, 'latitude': 0.003816217542651418, 'longitude': 3.365692632155995e-06, 'Macro_class': 0.0472682395825669}</t>
+          <t>{'const': 0.47963142281420623, 'N1ratio-ArgsPreds': -2.2257441617173854, 'Macro_class': 0.04142224926133391}</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>{'const': 2.3051876259872226e-98, 'N1ratio-ArgsPreds': 4.246817052101905e-110, 'latitude': 3.5475411217226984e-14, 'longitude': 0.9749639974986837, 'Macro_class': 2.3014751017305035e-22}</t>
+          <t>{'const': 9.45841271347944e-105, 'N1ratio-ArgsPreds': 4.596289885920894e-109, 'Macro_class': 2.3470991508836034e-21}</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': -0.5423510414787115, 'latitude': 0.16935299016552596, 'longitude': 0.0007150530267172963, 'Macro_class': 0.21312175304514197}</t>
+          <t>{'N1ratio-ArgsPreds': -0.4800871725308175, 'Macro_class': 0.19387483640395944}</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': np.float64(-0.5340076948730278), 'latitude': np.float64(0.1950173048898277), 'longitude': np.float64(0.0008156276106602306), 'Macro_class': np.float64(0.248825501044787)}</t>
+          <t>{'N1ratio-ArgsPreds': np.float64(-0.48897395336110305), 'Macro_class': np.float64(0.22078532851451926)}</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': np.float64(-0.5118082301460207), 'latitude': np.float64(0.16112230744976175), 'longitude': np.float64(0.0006609292242517679), 'Macro_class': np.float64(0.2081787909487982)}</t>
+          <t>{'N1ratio-ArgsPreds': np.float64(-0.48007116474832695), 'Macro_class': np.float64(0.19386837194002537)}</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': np.float64(26.194766444520212), 'latitude': np.float64(2.596039795793555), 'longitude': np.float64(4.368274394700436e-05), 'Macro_class': np.float64(4.333840900090342)}</t>
+          <t>{'N1ratio-ArgsPreds': np.float64(23.046832322281528), 'Macro_class': np.float64(3.7584945638676017)}</t>
         </is>
       </c>
       <c r="U3" t="n">
-        <v>0.06011049077604613</v>
+        <v>0.03758494563867598</v>
       </c>
       <c r="V3" t="n">
-        <v>45.19165994884488</v>
+        <v>92.34189557491651</v>
       </c>
       <c r="W3" t="n">
-        <v>6.069955880460317e-28</v>
+        <v>2.347099150885196e-21</v>
       </c>
     </row>
     <row r="4">
@@ -713,80 +713,80 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>['N1ratio-ArgsPreds', 'latitude', 'longitude', 'Macro_class', 'Fam_class']</t>
+          <t>['N1ratio-ArgsPreds', 'Macro_class', 'Fam_class']</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>1486</v>
+        <v>1805</v>
       </c>
       <c r="E4" t="n">
-        <v>1480</v>
+        <v>1801</v>
       </c>
       <c r="F4" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G4" t="n">
-        <v>0.3438200397117536</v>
+        <v>0.2668682982979526</v>
       </c>
       <c r="H4" t="n">
-        <v>155.0957632262547</v>
+        <v>218.5281780971398</v>
       </c>
       <c r="I4" t="n">
-        <v>1.21472196063553e-132</v>
+        <v>6.919535127744501e-121</v>
       </c>
       <c r="J4" t="n">
-        <v>152.3538590972354</v>
+        <v>194.896868848486</v>
       </c>
       <c r="K4" t="n">
-        <v>232.1830417227456</v>
+        <v>265.8415512465374</v>
       </c>
       <c r="L4" t="n">
-        <v>15.96583652510203</v>
+        <v>23.64822746601713</v>
       </c>
       <c r="M4" t="n">
-        <v>0.1029417966873212</v>
+        <v>0.1082159182945508</v>
       </c>
       <c r="N4" t="n">
-        <v>0.1563522166483135</v>
+        <v>0.1473622789614952</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>{'const': 0.5981575686294853, 'N1ratio-ArgsPreds': -0.2088218582386414, 'latitude': 0.0038290971737104007, 'longitude': -2.601538253564059e-05, 'Macro_class': 0.047902502946424536, 'Fam_class': -0.00025385066701125153}</t>
+          <t>{'const': 0.4849514239415572, 'N1ratio-ArgsPreds': -2.207511772190966, 'Macro_class': 0.04171775006190328, 'Fam_class': -0.0001723371552388445}</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>{'const': 6.886913643281096e-97, 'N1ratio-ArgsPreds': 1.2708412231894904e-100, 'latitude': 2.9775186991079475e-14, 'longitude': 0.8148211866376162, 'Macro_class': 1.462120673649917e-22, 'Fam_class': 0.3097802981023895}</t>
+          <t>{'const': 1.881976598398187e-99, 'N1ratio-ArgsPreds': 3.447747851221895e-103, 'Macro_class': 1.638210596866752e-21, 'Fam_class': 0.3774123439948174}</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': -0.5357052201930793, 'latitude': 0.1699245519299405, 'longitude': -0.005527057891617924, 'Macro_class': 0.21598150244963432, 'Fam_class': -0.022839054480706274}</t>
+          <t>{'N1ratio-ArgsPreds': -0.4761544939746868, 'Macro_class': 0.19525791362427602, 'Fam_class': -0.018296929237968818}</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': np.float64(-0.5137884196150758), 'latitude': np.float64(0.1956551665124548), 'longitude': np.float64(-0.0060889967102395175), 'Macro_class': np.float64(0.2500477546035998), 'Fam_class': np.float64(-0.026401283593912573)}</t>
+          <t>{'N1ratio-ArgsPreds': np.float64(-0.4771965953630288), 'Macro_class': np.float64(0.22169428095286267), 'Fam_class': np.float64(-0.02079968999636218)}</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': np.float64(-0.48512153557829313), 'latitude': np.float64(0.16161389278878238), 'longitude': np.float64(-0.004932479306926587), 'Macro_class': np.float64(0.20919646107349513), 'Fam_class': np.float64(-0.021393800127557823)}</t>
+          <t>{'N1ratio-ArgsPreds': np.float64(-0.46494328912941535), 'Macro_class': np.float64(0.1946655531744471), 'Fam_class': np.float64(-0.017813195159487066)}</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': np.float64(23.534290428184114), 'latitude': np.float64(2.611905034234405), 'longitude': np.float64(0.002432935211325898), 'Macro_class': np.float64(4.376315932567437), 'Fam_class': np.float64(0.04576946838978931)}</t>
+          <t>{'N1ratio-ArgsPreds': np.float64(21.61722621064791), 'Macro_class': np.float64(3.7894677592713486), 'Fam_class': np.float64(0.031730992178997344)}</t>
         </is>
       </c>
       <c r="U4" t="n">
-        <v>0.0004576946838985574</v>
+        <v>0.000317309921790021</v>
       </c>
       <c r="V4" t="n">
-        <v>1.032320663789096</v>
+        <v>0.7794986464465855</v>
       </c>
       <c r="W4" t="n">
-        <v>0.3097802981029886</v>
+        <v>0.3774123439945244</v>
       </c>
     </row>
     <row r="5">
@@ -798,80 +798,80 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>['N1ratio-ArgsPreds', 'latitude', 'longitude', 'Macro_class', 'Fam_class', 'Nlen_freq', 'Vlen_freq']</t>
+          <t>['N1ratio-ArgsPreds', 'Macro_class', 'Fam_class', 'Nlen_freq', 'Vlen_freq']</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>1486</v>
+        <v>1805</v>
       </c>
       <c r="E5" t="n">
-        <v>1478</v>
+        <v>1799</v>
       </c>
       <c r="F5" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G5" t="n">
-        <v>0.3534650481512172</v>
+        <v>0.2755305842342348</v>
       </c>
       <c r="H5" t="n">
-        <v>115.4332336610335</v>
+        <v>136.8393227513833</v>
       </c>
       <c r="I5" t="n">
-        <v>3.578062400881211e-135</v>
+        <v>3.617978631520469e-123</v>
       </c>
       <c r="J5" t="n">
-        <v>150.1144517003193</v>
+        <v>192.5940733178437</v>
       </c>
       <c r="K5" t="n">
-        <v>232.1830417227456</v>
+        <v>265.8415512465374</v>
       </c>
       <c r="L5" t="n">
-        <v>11.72408428891805</v>
+        <v>14.64949558573874</v>
       </c>
       <c r="M5" t="n">
-        <v>0.1015659348446003</v>
+        <v>0.1070561830560554</v>
       </c>
       <c r="N5" t="n">
-        <v>0.1563522166483135</v>
+        <v>0.1473622789614952</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>{'const': 0.6458937585888933, 'N1ratio-ArgsPreds': -0.20114649205907856, 'latitude': 0.003925164521142258, 'longitude': -0.00012710146272285695, 'Macro_class': 0.042297027722486495, 'Fam_class': -0.0004990434845918955, 'Nlen_freq': -0.052682622445800006, 'Vlen_freq': 0.04807378180068025}</t>
+          <t>{'const': 0.4980467588121588, 'N1ratio-ArgsPreds': -2.1511284754025217, 'Macro_class': 0.035227815052312164, 'Fam_class': -0.00034239971156991883, 'Nlen_freq': -0.44382234741068805, 'Vlen_freq': 0.5743810816476989}</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>{'const': 3.7954928616464696e-35, 'N1ratio-ArgsPreds': 2.3585894850431156e-92, 'latitude': 5.012573281164161e-15, 'longitude': 0.2615640702704981, 'Macro_class': 3.157615783892136e-16, 'Fam_class': 0.050688603012116876, 'Nlen_freq': 1.4809540184846517e-05, 'Vlen_freq': 5.002701251435402e-06}</t>
+          <t>{'const': 1.2425434064202673e-53, 'N1ratio-ArgsPreds': 5.82679153564602e-98, 'Macro_class': 4.525817707328598e-14, 'Fam_class': 0.0859880442849001, 'Nlen_freq': 6.586536210252003e-05, 'Vlen_freq': 4.008430018420318e-06}</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': -0.5160150701102927, 'latitude': 0.17418775033596007, 'longitude': -0.02700314483618067, 'Macro_class': 0.19070768821566006, 'Fam_class': -0.04489915849750601, 'Nlen_freq': -0.16614374439240998, 'Vlen_freq': 0.18469789822205665}</t>
+          <t>{'N1ratio-ArgsPreds': -0.4639927648780939, 'Macro_class': 0.16488208636490698, 'Fam_class': -0.03635236571598954, 'Nlen_freq': -0.1455617696926092, 'Vlen_freq': 0.17854009193854808}</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': np.float64(-0.49509730357606296), 'latitude': np.float64(0.2015222965011221), 'longitude': np.float64(-0.02920169921365487), 'Macro_class': np.float64(0.21009867671913646), 'Fam_class': np.float64(-0.050804707075893005), 'Nlen_freq': np.float64(-0.11233044011922146), 'Vlen_freq': np.float64(0.11833592707356501)}</t>
+          <t>{'N1ratio-ArgsPreds': np.float64(-0.46643005346458694), 'Macro_class': np.float64(0.1765108855249669), 'Fam_class': np.float64(-0.04046922026271198), 'Nlen_freq': np.float64(-0.09389408851482843), 'Vlen_freq': np.float64(0.1084057713708083)}</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': np.float64(-0.45819251560883245), 'latitude': np.float64(0.1654328660103413), 'longitude': np.float64(-0.023490343970074736), 'Macro_class': np.float64(0.1727915527460518), 'Fam_class': np.float64(-0.0409035651729574), 'Nlen_freq': np.float64(-0.09089728042639116), 'Vlen_freq': np.float64(0.09582413573929108)}</t>
+          <t>{'N1ratio-ArgsPreds': np.float64(-0.4488179288681617), 'Macro_class': np.float64(0.15263517026810833), 'Fam_class': np.float64(-0.03447392963613354), 'Nlen_freq': np.float64(-0.08027330772063883), 'Vlen_freq': np.float64(0.09281740421548773)}</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': np.float64(20.994038135995016), 'latitude': np.float64(2.7368033156395537), 'longitude': np.float64(0.05517962598324265), 'Macro_class': np.float64(2.9856920700391596), 'Fam_class': np.float64(0.16731016438583737), 'Nlen_freq': np.float64(0.8262315588913993), 'Vlen_freq': np.float64(0.9182264990182081)}</t>
+          <t>{'N1ratio-ArgsPreds': np.float64(20.143753327350623), 'Macro_class': np.float64(2.329749520277442), 'Fam_class': np.float64(0.11884518245570866), 'Nlen_freq': np.float64(0.6443803932412373), 'Vlen_freq': np.float64(0.8615070525301239)}</t>
         </is>
       </c>
       <c r="U5" t="n">
-        <v>0.009645008439463587</v>
+        <v>0.008662285936282266</v>
       </c>
       <c r="V5" t="n">
-        <v>11.02440203175693</v>
+        <v>10.75507955218514</v>
       </c>
       <c r="W5" t="n">
-        <v>1.768170994010267e-05</v>
+        <v>2.274216811341173e-05</v>
       </c>
     </row>
   </sheetData>

--- a/scripts/checks/results/HLR_results_04_>1_lg_families_tPBC.xlsx
+++ b/scripts/checks/results/HLR_results_04_>1_lg_families_tPBC.xlsx
@@ -562,57 +562,57 @@
         <v>1</v>
       </c>
       <c r="G2" t="n">
-        <v>0.2289660427374866</v>
+        <v>0.2230905752383499</v>
       </c>
       <c r="H2" t="n">
-        <v>535.4184094840506</v>
+        <v>517.7338494485975</v>
       </c>
       <c r="I2" t="n">
-        <v>6.165311118376326e-104</v>
+        <v>5.857522915737756e-101</v>
       </c>
       <c r="J2" t="n">
-        <v>204.972863262423</v>
+        <v>205.036942502581</v>
       </c>
       <c r="K2" t="n">
-        <v>265.8415512465374</v>
+        <v>263.9135734072023</v>
       </c>
       <c r="L2" t="n">
-        <v>60.86868798411442</v>
+        <v>58.87663090462121</v>
       </c>
       <c r="M2" t="n">
-        <v>0.113684339025193</v>
+        <v>0.113719879369152</v>
       </c>
       <c r="N2" t="n">
-        <v>0.1473622789614952</v>
+        <v>0.1462935551037707</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>{'const': 0.5718717535467436, 'N1ratio-ArgsPreds': -2.218404205002331}</t>
+          <t>{'const': 0.5587190655100238, 'N1ratio-ArgsPreds': -2.145662524819709}</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>{'const': 1.6885341073455672e-165, 'N1ratio-ArgsPreds': 6.1653111183735e-104}</t>
+          <t>{'const': 3.9637284724572447e-162, 'N1ratio-ArgsPreds': 5.857522915737049e-101}</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': -0.478503963136657}</t>
+          <t>{'N1ratio-ArgsPreds': -0.47232465025483217}</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': np.float64(-0.4785039631366576)}</t>
+          <t>{'N1ratio-ArgsPreds': np.float64(-0.47232465025483383)}</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': np.float64(-0.47850396313665755)}</t>
+          <t>{'N1ratio-ArgsPreds': np.float64(-0.4723246502548339)}</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': np.float64(22.89660427374877)}</t>
+          <t>{'N1ratio-ArgsPreds': np.float64(22.309057523835115)}</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
@@ -641,67 +641,67 @@
         <v>2</v>
       </c>
       <c r="G3" t="n">
-        <v>0.2665509883761625</v>
+        <v>0.2612927581108083</v>
       </c>
       <c r="H3" t="n">
-        <v>327.4425852660282</v>
+        <v>318.6983444967401</v>
       </c>
       <c r="I3" t="n">
-        <v>4.992347745244783e-122</v>
+        <v>3.115970412755871e-119</v>
       </c>
       <c r="J3" t="n">
-        <v>194.9812230103206</v>
+        <v>194.9548679087551</v>
       </c>
       <c r="K3" t="n">
-        <v>265.8415512465374</v>
+        <v>263.9135734072023</v>
       </c>
       <c r="L3" t="n">
-        <v>35.43016411810841</v>
+        <v>34.47935274922358</v>
       </c>
       <c r="M3" t="n">
-        <v>0.1082026764763155</v>
+        <v>0.1081880510037487</v>
       </c>
       <c r="N3" t="n">
-        <v>0.1473622789614952</v>
+        <v>0.1462935551037707</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>{'const': 0.47963142281420623, 'N1ratio-ArgsPreds': -2.2257441617173854, 'Macro_class': 0.04142224926133391}</t>
+          <t>{'const': 0.46561616785546445, 'N1ratio-ArgsPreds': -2.1504862354866936, 'Macro_class': 0.041608510015139766}</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>{'const': 9.45841271347944e-105, 'N1ratio-ArgsPreds': 4.596289885920894e-109, 'Macro_class': 2.3470991508836034e-21}</t>
+          <t>{'const': 8.642872504147453e-101, 'N1ratio-ArgsPreds': 8.302772214528263e-106, 'Macro_class': 1.561272957374003e-21}</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': -0.4800871725308175, 'Macro_class': 0.19387483640395944}</t>
+          <t>{'N1ratio-ArgsPreds': -0.4733864935910322, 'Macro_class': 0.19545667137176415}</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': np.float64(-0.48897395336110305), 'Macro_class': np.float64(0.22078532851451926)}</t>
+          <t>{'N1ratio-ArgsPreds': np.float64(-0.4824390464932575), 'Macro_class': np.float64(0.22174758290473814)}</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': np.float64(-0.48007116474832695), 'Macro_class': np.float64(0.19386837194002537)}</t>
+          <t>{'N1ratio-ArgsPreds': np.float64(-0.4733795079065503), 'Macro_class': np.float64(0.19545378705069635)}</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': np.float64(23.046832322281528), 'Macro_class': np.float64(3.7584945638676017)}</t>
+          <t>{'N1ratio-ArgsPreds': np.float64(22.408815850584773), 'Macro_class': np.float64(3.820218287245896)}</t>
         </is>
       </c>
       <c r="U3" t="n">
-        <v>0.03758494563867598</v>
+        <v>0.03820218287245847</v>
       </c>
       <c r="V3" t="n">
-        <v>92.34189557491651</v>
+        <v>93.19027841139862</v>
       </c>
       <c r="W3" t="n">
-        <v>2.347099150885196e-21</v>
+        <v>1.561272957375961e-21</v>
       </c>
     </row>
     <row r="4">
@@ -726,67 +726,67 @@
         <v>3</v>
       </c>
       <c r="G4" t="n">
-        <v>0.2668682982979526</v>
+        <v>0.2617402977261598</v>
       </c>
       <c r="H4" t="n">
-        <v>218.5281780971398</v>
+        <v>212.840312044176</v>
       </c>
       <c r="I4" t="n">
-        <v>6.919535127744501e-121</v>
+        <v>3.646215143978709e-118</v>
       </c>
       <c r="J4" t="n">
-        <v>194.896868848486</v>
+        <v>194.8367561296264</v>
       </c>
       <c r="K4" t="n">
-        <v>265.8415512465374</v>
+        <v>263.9135734072023</v>
       </c>
       <c r="L4" t="n">
-        <v>23.64822746601713</v>
+        <v>23.02560575919195</v>
       </c>
       <c r="M4" t="n">
-        <v>0.1082159182945508</v>
+        <v>0.1081825408826354</v>
       </c>
       <c r="N4" t="n">
-        <v>0.1473622789614952</v>
+        <v>0.1462935551037707</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>{'const': 0.4849514239415572, 'N1ratio-ArgsPreds': -2.207511772190966, 'Macro_class': 0.04171775006190328, 'Fam_class': -0.0001723371552388445}</t>
+          <t>{'const': 0.47201951210648324, 'N1ratio-ArgsPreds': -2.129686796291047, 'Macro_class': 0.04196067513939902, 'Fam_class': -0.00020374127044691596}</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>{'const': 1.881976598398187e-99, 'N1ratio-ArgsPreds': 3.447747851221895e-103, 'Macro_class': 1.638210596866752e-21, 'Fam_class': 0.3774123439948174}</t>
+          <t>{'const': 8.484546750376526e-96, 'N1ratio-ArgsPreds': 5.302069347400777e-100, 'Macro_class': 9.604855698725348e-22, 'Fam_class': 0.29621687497276633}</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': -0.4761544939746868, 'Macro_class': 0.19525791362427602, 'Fam_class': -0.018296929237968818}</t>
+          <t>{'N1ratio-ArgsPreds': -0.4688079134415718, 'Macro_class': 0.19711097293016874, 'Fam_class': -0.021709952152286646}</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': np.float64(-0.4771965953630288), 'Macro_class': np.float64(0.22169428095286267), 'Fam_class': np.float64(-0.02079968999636218)}</t>
+          <t>{'N1ratio-ArgsPreds': np.float64(-0.47054188077538556), 'Macro_class': np.float64(0.22294872685681663), 'Fam_class': np.float64(-0.0246138508046279)}</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': np.float64(-0.46494328912941535), 'Macro_class': np.float64(0.1946655531744471), 'Fam_class': np.float64(-0.017813195159487066)}</t>
+          <t>{'N1ratio-ArgsPreds': np.float64(-0.4581929055970471), 'Macro_class': np.float64(0.1965081719037516), 'Fam_class': np.float64(-0.021155132127956066)}</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': np.float64(21.61722621064791), 'Macro_class': np.float64(3.7894677592713486), 'Fam_class': np.float64(0.031730992178997344)}</t>
+          <t>{'N1ratio-ArgsPreds': np.float64(20.994073873946455), 'Macro_class': np.float64(3.861546162495439), 'Fam_class': np.float64(0.044753961535127895)}</t>
         </is>
       </c>
       <c r="U4" t="n">
-        <v>0.000317309921790021</v>
+        <v>0.0004475396153514888</v>
       </c>
       <c r="V4" t="n">
-        <v>0.7794986464465855</v>
+        <v>1.091782261398655</v>
       </c>
       <c r="W4" t="n">
-        <v>0.3774123439945244</v>
+        <v>0.2962168749725353</v>
       </c>
     </row>
     <row r="5">
@@ -811,67 +811,67 @@
         <v>5</v>
       </c>
       <c r="G5" t="n">
-        <v>0.2755305842342348</v>
+        <v>0.2717040675328668</v>
       </c>
       <c r="H5" t="n">
-        <v>136.8393227513833</v>
+        <v>134.2299457408231</v>
       </c>
       <c r="I5" t="n">
-        <v>3.617978631520469e-123</v>
+        <v>4.048499415195277e-121</v>
       </c>
       <c r="J5" t="n">
-        <v>192.5940733178437</v>
+        <v>192.2071820353316</v>
       </c>
       <c r="K5" t="n">
-        <v>265.8415512465374</v>
+        <v>263.9135734072023</v>
       </c>
       <c r="L5" t="n">
-        <v>14.64949558573874</v>
+        <v>14.34127827437413</v>
       </c>
       <c r="M5" t="n">
-        <v>0.1070561830560554</v>
+        <v>0.1068411239773939</v>
       </c>
       <c r="N5" t="n">
-        <v>0.1473622789614952</v>
+        <v>0.1462935551037707</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>{'const': 0.4980467588121588, 'N1ratio-ArgsPreds': -2.1511284754025217, 'Macro_class': 0.035227815052312164, 'Fam_class': -0.00034239971156991883, 'Nlen_freq': -0.44382234741068805, 'Vlen_freq': 0.5743810816476989}</t>
+          <t>{'const': 0.4901173108997145, 'N1ratio-ArgsPreds': -2.073469102288052, 'Macro_class': 0.03521066658324583, 'Fam_class': -0.0003778693762795785, 'Nlen_freq': -0.4814909423293307, 'Vlen_freq': 0.6092779611926791}</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>{'const': 1.2425434064202673e-53, 'N1ratio-ArgsPreds': 5.82679153564602e-98, 'Macro_class': 4.525817707328598e-14, 'Fam_class': 0.0859880442849001, 'Nlen_freq': 6.586536210252003e-05, 'Vlen_freq': 4.008430018420318e-06}</t>
+          <t>{'const': 2.79131044212699e-52, 'N1ratio-ArgsPreds': 6.190586659118367e-95, 'Macro_class': 4.245562584459819e-14, 'Fam_class': 0.05761055973300836, 'Nlen_freq': 1.3739064374917188e-05, 'Vlen_freq': 8.905102646210644e-07}</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': -0.4639927648780939, 'Macro_class': 0.16488208636490698, 'Fam_class': -0.03635236571598954, 'Nlen_freq': -0.1455617696926092, 'Vlen_freq': 0.17854009193854808}</t>
+          <t>{'N1ratio-ArgsPreds': -0.45643271354366205, 'Macro_class': 0.165402694896743, 'Fam_class': -0.04026442978807991, 'Nlen_freq': -0.15867049025685148, 'Vlen_freq': 0.19035569947453146}</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': np.float64(-0.46643005346458694), 'Macro_class': np.float64(0.1765108855249669), 'Fam_class': np.float64(-0.04046922026271198), 'Nlen_freq': np.float64(-0.09389408851482843), 'Vlen_freq': np.float64(0.1084057713708083)}</t>
+          <t>{'N1ratio-ArgsPreds': np.float64(-0.45987423072487094), 'Macro_class': np.float64(0.1767026073237232), 'Fam_class': np.float64(-0.04474783222068816), 'Nlen_freq': np.float64(-0.10225699191175704), 'Vlen_freq': np.float64(0.1154940386865131)}</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': np.float64(-0.4488179288681617), 'Macro_class': np.float64(0.15263517026810833), 'Fam_class': np.float64(-0.03447392963613354), 'Nlen_freq': np.float64(-0.08027330772063883), 'Vlen_freq': np.float64(0.09281740421548773)}</t>
+          <t>{'N1ratio-ArgsPreds': np.float64(-0.44196496762325943), 'Macro_class': np.float64(0.15320931543352032), 'Fam_class': np.float64(-0.038226205303686506), 'Nlen_freq': np.float64(-0.08772623852011296), 'Vlen_freq': np.float64(0.09922691783022826)}</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': np.float64(20.143753327350623), 'Macro_class': np.float64(2.329749520277442), 'Fam_class': np.float64(0.11884518245570866), 'Nlen_freq': np.float64(0.6443803932412373), 'Vlen_freq': np.float64(0.8615070525301239)}</t>
+          <t>{'N1ratio-ArgsPreds': np.float64(19.533303260622876), 'Macro_class': np.float64(2.3473094335607927), 'Fam_class': np.float64(0.14612427719195903), 'Nlen_freq': np.float64(0.7695892924887752), 'Vlen_freq': np.float64(0.9845981222086871)}</t>
         </is>
       </c>
       <c r="U5" t="n">
-        <v>0.008662285936282266</v>
+        <v>0.00996376980670699</v>
       </c>
       <c r="V5" t="n">
-        <v>10.75507955218514</v>
+        <v>12.30600164245377</v>
       </c>
       <c r="W5" t="n">
-        <v>2.274216811341173e-05</v>
+        <v>4.918126932642786e-06</v>
       </c>
     </row>
   </sheetData>

--- a/scripts/checks/results/HLR_results_04_>1_lg_families_tPBC.xlsx
+++ b/scripts/checks/results/HLR_results_04_>1_lg_families_tPBC.xlsx
@@ -562,57 +562,57 @@
         <v>1</v>
       </c>
       <c r="G2" t="n">
-        <v>0.2230905752383499</v>
+        <v>0.2229212985647023</v>
       </c>
       <c r="H2" t="n">
-        <v>517.7338494485975</v>
+        <v>517.2283072097867</v>
       </c>
       <c r="I2" t="n">
-        <v>5.857522915737756e-101</v>
+        <v>7.131389721807892e-101</v>
       </c>
       <c r="J2" t="n">
-        <v>205.036942502581</v>
+        <v>205.0816169144178</v>
       </c>
       <c r="K2" t="n">
-        <v>263.9135734072023</v>
+        <v>263.9135734072022</v>
       </c>
       <c r="L2" t="n">
-        <v>58.87663090462121</v>
+        <v>58.8319564927844</v>
       </c>
       <c r="M2" t="n">
-        <v>0.113719879369152</v>
+        <v>0.1137446571904702</v>
       </c>
       <c r="N2" t="n">
-        <v>0.1462935551037707</v>
+        <v>0.1462935551037706</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>{'const': 0.5587190655100238, 'N1ratio-ArgsPreds': -2.145662524819709}</t>
+          <t>{'const': 0.5582554068474909, 'N1ratio-ArgsPreds': -2.1419111097183157}</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>{'const': 3.9637284724572447e-162, 'N1ratio-ArgsPreds': 5.857522915737049e-101}</t>
+          <t>{'const': 4.624050485653135e-162, 'N1ratio-ArgsPreds': 7.131389721806646e-101}</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': -0.47232465025483217}</t>
+          <t>{'N1ratio-ArgsPreds': -0.47214542099304796}</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': np.float64(-0.47232465025483383)}</t>
+          <t>{'N1ratio-ArgsPreds': np.float64(-0.47214542099304907)}</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': np.float64(-0.4723246502548339)}</t>
+          <t>{'N1ratio-ArgsPreds': np.float64(-0.47214542099304924)}</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': np.float64(22.309057523835115)}</t>
+          <t>{'N1ratio-ArgsPreds': np.float64(22.292129856470368)}</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
@@ -641,67 +641,67 @@
         <v>2</v>
       </c>
       <c r="G3" t="n">
-        <v>0.2612927581108083</v>
+        <v>0.2611623770544381</v>
       </c>
       <c r="H3" t="n">
-        <v>318.6983444967401</v>
+        <v>318.4831070025062</v>
       </c>
       <c r="I3" t="n">
-        <v>3.115970412755871e-119</v>
+        <v>3.653012461218936e-119</v>
       </c>
       <c r="J3" t="n">
-        <v>194.9548679087551</v>
+        <v>194.9892772392463</v>
       </c>
       <c r="K3" t="n">
-        <v>263.9135734072023</v>
+        <v>263.9135734072022</v>
       </c>
       <c r="L3" t="n">
-        <v>34.47935274922358</v>
+        <v>34.46214808397794</v>
       </c>
       <c r="M3" t="n">
-        <v>0.1081880510037487</v>
+        <v>0.1082071460817127</v>
       </c>
       <c r="N3" t="n">
-        <v>0.1462935551037707</v>
+        <v>0.1462935551037706</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>{'const': 0.46561616785546445, 'N1ratio-ArgsPreds': -2.1504862354866936, 'Macro_class': 0.041608510015139766}</t>
+          <t>{'const': 0.46513774167418365, 'N1ratio-ArgsPreds': -2.1469189790826846, 'Macro_class': 0.04162973545766315}</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>{'const': 8.642872504147453e-101, 'N1ratio-ArgsPreds': 8.302772214528263e-106, 'Macro_class': 1.561272957374003e-21}</t>
+          <t>{'const': 1.0593309472334485e-100, 'N1ratio-ArgsPreds': 9.736586677082173e-106, 'Macro_class': 1.5035499788850336e-21}</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': -0.4733864935910322, 'Macro_class': 0.19545667137176415}</t>
+          <t>{'N1ratio-ArgsPreds': -0.47324931488415767, 'Macro_class': 0.19555637824284666}</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': np.float64(-0.4824390464932575), 'Macro_class': np.float64(0.22174758290473814)}</t>
+          <t>{'N1ratio-ArgsPreds': np.float64(-0.4822986774862637), 'Macro_class': np.float64(0.2218362744759916)}</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': np.float64(-0.4733795079065503), 'Macro_class': np.float64(0.19545378705069635)}</t>
+          <t>{'N1ratio-ArgsPreds': np.float64(-0.47324177483552493), 'Macro_class': np.float64(0.1955532625392281)}</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': np.float64(22.408815850584773), 'Macro_class': np.float64(3.820218287245896)}</t>
+          <t>{'N1ratio-ArgsPreds': np.float64(22.395777744947768), 'Macro_class': np.float64(3.8241078489736275)}</t>
         </is>
       </c>
       <c r="U3" t="n">
-        <v>0.03820218287245847</v>
+        <v>0.03824107848973579</v>
       </c>
       <c r="V3" t="n">
-        <v>93.19027841139862</v>
+        <v>93.26869842357944</v>
       </c>
       <c r="W3" t="n">
-        <v>1.561272957375961e-21</v>
+        <v>1.503549978886658e-21</v>
       </c>
     </row>
     <row r="4">
@@ -726,67 +726,67 @@
         <v>3</v>
       </c>
       <c r="G4" t="n">
-        <v>0.2617402977261598</v>
+        <v>0.2616068682341256</v>
       </c>
       <c r="H4" t="n">
-        <v>212.840312044176</v>
+        <v>212.6933695256576</v>
       </c>
       <c r="I4" t="n">
-        <v>3.646215143978709e-118</v>
+        <v>4.289512620978463e-118</v>
       </c>
       <c r="J4" t="n">
-        <v>194.8367561296264</v>
+        <v>194.871969983667</v>
       </c>
       <c r="K4" t="n">
-        <v>263.9135734072023</v>
+        <v>263.9135734072022</v>
       </c>
       <c r="L4" t="n">
-        <v>23.02560575919195</v>
+        <v>23.01386780784506</v>
       </c>
       <c r="M4" t="n">
-        <v>0.1081825408826354</v>
+        <v>0.1082020932724414</v>
       </c>
       <c r="N4" t="n">
-        <v>0.1462935551037707</v>
+        <v>0.1462935551037706</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>{'const': 0.47201951210648324, 'N1ratio-ArgsPreds': -2.129686796291047, 'Macro_class': 0.04196067513939902, 'Fam_class': -0.00020374127044691596}</t>
+          <t>{'const': 0.4715194025912471, 'N1ratio-ArgsPreds': -2.126197072589081, 'Macro_class': 0.04198050396622751, 'Fam_class': -0.00020305575605360327}</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>{'const': 8.484546750376526e-96, 'N1ratio-ArgsPreds': 5.302069347400777e-100, 'Macro_class': 9.604855698725348e-22, 'Fam_class': 0.29621687497276633}</t>
+          <t>{'const': 1.0653031829244388e-95, 'N1ratio-ArgsPreds': 6.241064765796746e-100, 'Macro_class': 9.276610556451246e-22, 'Fam_class': 0.29791086649945603}</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': -0.4688079134415718, 'Macro_class': 0.19711097293016874, 'Fam_class': -0.021709952152286646}</t>
+          <t>{'N1ratio-ArgsPreds': -0.4686815467723952, 'Macro_class': 0.19720411917567704, 'Fam_class': -0.021636906153084445}</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': np.float64(-0.47054188077538556), 'Macro_class': np.float64(0.22294872685681663), 'Fam_class': np.float64(-0.0246138508046279)}</t>
+          <t>{'N1ratio-ArgsPreds': np.float64(-0.47039232870856956), 'Macro_class': np.float64(0.22303015987903108), 'Fam_class': np.float64(-0.024527713941786412)}</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': np.float64(-0.4581929055970471), 'Macro_class': np.float64(0.1965081719037516), 'Fam_class': np.float64(-0.021155132127956066)}</t>
+          <t>{'N1ratio-ArgsPreds': np.float64(-0.45804727839757897), 'Macro_class': np.float64(0.1966014678451712), 'Fam_class': np.float64(-0.021082959462260426)}</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': np.float64(20.994073873946455), 'Macro_class': np.float64(3.861546162495439), 'Fam_class': np.float64(0.044753961535127895)}</t>
+          <t>{'N1ratio-ArgsPreds': np.float64(20.98073092474292), 'Macro_class': np.float64(3.865213715887589), 'Fam_class': np.float64(0.04444911796873165)}</t>
         </is>
       </c>
       <c r="U4" t="n">
-        <v>0.0004475396153514888</v>
+        <v>0.0004444911796874784</v>
       </c>
       <c r="V4" t="n">
-        <v>1.091782261398655</v>
+        <v>1.084149594813642</v>
       </c>
       <c r="W4" t="n">
-        <v>0.2962168749725353</v>
+        <v>0.2979108664999431</v>
       </c>
     </row>
     <row r="5">
@@ -811,67 +811,67 @@
         <v>5</v>
       </c>
       <c r="G5" t="n">
-        <v>0.2717040675328668</v>
+        <v>0.2715872720337372</v>
       </c>
       <c r="H5" t="n">
-        <v>134.2299457408231</v>
+        <v>134.150731756934</v>
       </c>
       <c r="I5" t="n">
-        <v>4.048499415195277e-121</v>
+        <v>4.673665264680472e-121</v>
       </c>
       <c r="J5" t="n">
-        <v>192.2071820353316</v>
+        <v>192.2380059528647</v>
       </c>
       <c r="K5" t="n">
-        <v>263.9135734072023</v>
+        <v>263.9135734072022</v>
       </c>
       <c r="L5" t="n">
-        <v>14.34127827437413</v>
+        <v>14.3351134908675</v>
       </c>
       <c r="M5" t="n">
-        <v>0.1068411239773939</v>
+        <v>0.1068582578948664</v>
       </c>
       <c r="N5" t="n">
-        <v>0.1462935551037707</v>
+        <v>0.1462935551037706</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>{'const': 0.4901173108997145, 'N1ratio-ArgsPreds': -2.073469102288052, 'Macro_class': 0.03521066658324583, 'Fam_class': -0.0003778693762795785, 'Nlen_freq': -0.4814909423293307, 'Vlen_freq': 0.6092779611926791}</t>
+          <t>{'const': 0.4899926038435321, 'N1ratio-ArgsPreds': -2.0699832575520745, 'Macro_class': 0.035237882499417096, 'Fam_class': -0.00037675014764283673, 'Nlen_freq': -0.48903187903968354, 'Vlen_freq': 0.6096321626398411}</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>{'const': 2.79131044212699e-52, 'N1ratio-ArgsPreds': 6.190586659118367e-95, 'Macro_class': 4.245562584459819e-14, 'Fam_class': 0.05761055973300836, 'Nlen_freq': 1.3739064374917188e-05, 'Vlen_freq': 8.905102646210644e-07}</t>
+          <t>{'const': 2.7350789361078727e-52, 'N1ratio-ArgsPreds': 7.542952142368486e-95, 'Macro_class': 4.081031593985169e-14, 'Fam_class': 0.0583886117878278, 'Nlen_freq': 1.2980441262438646e-05, 'Vlen_freq': 8.828742798608325e-07}</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': -0.45643271354366205, 'Macro_class': 0.165402694896743, 'Fam_class': -0.04026442978807991, 'Nlen_freq': -0.15867049025685148, 'Vlen_freq': 0.19035569947453146}</t>
+          <t>{'N1ratio-ArgsPreds': -0.4562902317239555, 'Macro_class': 0.16553054211793006, 'Fam_class': -0.04014516872674545, 'Nlen_freq': -0.15919120806340695, 'Vlen_freq': 0.1905025642310229}</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': np.float64(-0.45987423072487094), 'Macro_class': np.float64(0.1767026073237232), 'Fam_class': np.float64(-0.04474783222068816), 'Nlen_freq': np.float64(-0.10225699191175704), 'Vlen_freq': np.float64(0.1154940386865131)}</t>
+          <t>{'N1ratio-ArgsPreds': np.float64(-0.4596862415685414), 'Macro_class': np.float64(0.17682104275351457), 'Fam_class': np.float64(-0.0446093717477114), 'Nlen_freq': np.float64(-0.10254811473670201), 'Vlen_freq': np.float64(0.11553342119602678)}</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': np.float64(-0.44196496762325943), 'Macro_class': np.float64(0.15320931543352032), 'Fam_class': np.float64(-0.038226205303686506), 'Nlen_freq': np.float64(-0.08772623852011296), 'Vlen_freq': np.float64(0.09922691783022826)}</t>
+          <t>{'N1ratio-ArgsPreds': np.float64(-0.44177129971954315), 'Macro_class': np.float64(0.15332761049202123), 'Fam_class': np.float64(-0.038110743594060734), 'Nlen_freq': np.float64(-0.0879856974470508), 'Vlen_freq': np.float64(0.09926916990476457)}</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': np.float64(19.533303260622876), 'Macro_class': np.float64(2.3473094335607927), 'Fam_class': np.float64(0.14612427719195903), 'Nlen_freq': np.float64(0.7695892924887752), 'Vlen_freq': np.float64(0.9845981222086871)}</t>
+          <t>{'N1ratio-ArgsPreds': np.float64(19.516188125589444), 'Macro_class': np.float64(2.350935613919298), 'Fam_class': np.float64(0.14524287772922412), 'Nlen_freq': np.float64(0.7741482955243962), 'Vlen_freq': np.float64(0.9854368093581016)}</t>
         </is>
       </c>
       <c r="U5" t="n">
-        <v>0.00996376980670699</v>
+        <v>0.009980403799611626</v>
       </c>
       <c r="V5" t="n">
-        <v>12.30600164245377</v>
+        <v>12.32456940011962</v>
       </c>
       <c r="W5" t="n">
-        <v>4.918126932642786e-06</v>
+        <v>4.828861753142112e-06</v>
       </c>
     </row>
   </sheetData>
